--- a/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.95%1,034,000</t>
+          <t>8.78%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>8.78%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.09%413,000</t>
+          <t>6.94%413,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>6.94%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6875</v>
+        <v>1305</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.24%221,000</t>
+          <t>5.36%1,209,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.36%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>221000</v>
+        <v>1209000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.37%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1215</v>
+        <v>6800</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.07%1,209,000</t>
+          <t>5.10%221,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>5.10%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1209000</v>
+        <v>221000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.02%123,000</t>
+          <t>5.07%123,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>5.07%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.84%282,000</t>
+          <t>4.97%282,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.56%377,000</t>
+          <t>4.40%377,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.56%</t>
+          <t>4.40%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.39%669,000</t>
+          <t>4.28%669,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.28%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.22%155,000</t>
+          <t>4.16%155,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.16%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.65%4,167,000</t>
+          <t>3.68%4,167,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.68%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+4.83%1085</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2080</v>
+        <v>1085</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.37%470,000</t>
+          <t>3.57%884,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>470000</v>
+        <v>884000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.83%1085</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.83%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1085</v>
+        <v>2190</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.31%884,000</t>
+          <t>3.50%470,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>884000</v>
+        <v>470000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>-1.85%5030</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-1.85%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2110</v>
+        <v>5030</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.19%438,197</t>
+          <t>3.26%181,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.26%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>438197</v>
+        <v>181000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.85%5030</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5030</v>
+        <v>2085</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.14%181,000</t>
+          <t>3.10%438,197</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>181000</v>
+        <v>438197</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:05</t>
+          <t>2026-10-02 19:06:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.11%47,400</t>
+          <t>3.03%47,400</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.62%596,000</t>
+          <t>2.74%596,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.60%295,000</t>
+          <t>2.54%295,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.19%94.2</t>
+          <t>+6.16%100</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.00%6,147,000</t>
+          <t>2.09%6,147,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.76%529</t>
+          <t>+2.46%542</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.89%1,034,000</t>
+          <t>1.90%1,034,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3.41%212.5</t>
+          <t>+0.47%213.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3.41%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>212.5</v>
+        <v>213.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.62%2,208,000</t>
+          <t>1.60%2,208,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.33%150.5</t>
+          <t>0%150.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.61%3,104,000</t>
+          <t>1.59%3,104,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.48%132,000</t>
+          <t>1.42%132,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.23%1095</t>
+          <t>+0.91%1105</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1095</v>
+        <v>1105</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.43%378,000</t>
+          <t>1.42%378,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+7.71%852</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+7.71%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>852</v>
+        <v>161.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.19%404,000</t>
+          <t>1.15%2,096,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>404000</v>
+        <v>2096000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>-2%835</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>161.5</v>
+        <v>835</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.17%2,096,000</t>
+          <t>1.15%404,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2096000</v>
+        <v>404000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.14%464,000</t>
+          <t>1.12%464,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.51%296</t>
+          <t>-0.17%295.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>296</v>
+        <v>295.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.02%999,000</t>
+          <t>1.00%999,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.63%238</t>
+          <t>+0.84%240</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.96%1,169,000</t>
+          <t>0.95%1,169,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.88%224.5</t>
+          <t>+0.67%226</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>224.5</v>
+        <v>226</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.86%1,107,336</t>
+          <t>0.85%1,107,336</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:06</t>
+          <t>2026-10-02 19:06:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,34 +2273,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.99%254</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>254</v>
+        <v>6290</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.84%960,000</t>
+          <t>0.83%39,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>960000</v>
+        <v>39000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>-1.18%251</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6205</v>
+        <v>251</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.83%39,000</t>
+          <t>0.82%960,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>39000</v>
+        <v>960000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.04%1895</t>
+          <t>-1.3%2660</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1895</v>
+        <v>2660</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.80%122,000</t>
+          <t>0.81%82,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>122000</v>
+        <v>82000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.3%2660</t>
+          <t>-0.53%1885</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2660</v>
+        <v>1885</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.75%82,000</t>
+          <t>0.78%122,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>82000</v>
+        <v>122000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.53%340,000</t>
+          <t>0.54%340,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+2.16%567</t>
+          <t>+2.82%583</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.16%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.39%200,000</t>
+          <t>0.40%200,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+9.92%975</t>
+          <t>+0.62%981</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.39%115,000</t>
+          <t>0.38%115,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.37%133,000</t>
+          <t>0.36%133,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+4.97%169</t>
+          <t>+2.66%173.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+4.97%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>169</v>
+        <v>173.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.34%592,000</t>
+          <t>0.35%592,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.14%95.3</t>
+          <t>+3.67%98.8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+3.67%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>95.3</v>
+        <v>98.8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.27%834,000</t>
+          <t>0.28%834,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.77%230.5</t>
+          <t>+1.74%234.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.77%</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>230.5</v>
+        <v>234.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.27%5490</t>
+          <t>+1.64%5580</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5490</v>
+        <v>5580</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.19%124.5</t>
+          <t>0%124.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.48%105.5</t>
+          <t>-0.47%105</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>105.5</v>
+        <v>105</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:28:07</t>
+          <t>2026-10-02 19:06:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.61%67.4</t>
+          <t>-0.89%66.8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>67.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.06%241,040</t>
+          <t>0.05%241,040</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K46" t="n">

--- a/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:39</t>
+          <t>2026-10-02 22:51:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:41</t>
+          <t>2026-10-02 22:51:12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:42</t>
+          <t>2026-10-02 22:51:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:11</t>
+          <t>2026-10-02 23:00:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:12</t>
+          <t>2026-10-02 23:00:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:14</t>
+          <t>2026-10-02 23:00:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:18</t>
+          <t>2026-10-02 23:49:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:20</t>
+          <t>2026-10-02 23:49:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:21</t>
+          <t>2026-10-02 23:49:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
